--- a/Paradigmas/Atv-16_06_integracao_excel/funcionarios.xlsx
+++ b/Paradigmas/Atv-16_06_integracao_excel/funcionarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasnarita/Documents/IDP Projects/Paradigmas/Atv-16_06_integracao_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01279086-1F6C-3949-A630-B5155C57F062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2C3D5A-83B6-BE4A-A1A5-0934C925E927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,13 +40,13 @@
     <t>Carla</t>
   </si>
   <si>
-    <t>Maria</t>
-  </si>
-  <si>
     <t>Ana</t>
   </si>
   <si>
-    <t>Joao</t>
+    <t>Claudio</t>
+  </si>
+  <si>
+    <t>Mariana</t>
   </si>
 </sst>
 </file>
@@ -439,7 +439,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>2500</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>2400</v>
@@ -461,10 +461,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>2600</v>
+        <v>7600</v>
       </c>
       <c r="C4">
         <v>28</v>
@@ -475,7 +475,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -497,7 +497,7 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -506,7 +506,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 B7:C7 B6:C6 B5:C5 B4:C4 B3:C3 B2:C2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 C7 C6 C5 C4 B3:C3 B2:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>